--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 211154억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 211155억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 223387억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 223444억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 229550억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 229661억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 230991억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 231772억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 229924억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 230745억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 227931억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 228737억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 224978억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 225771억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 221965억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 222128억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1809,49 +1809,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 211154억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 211155억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 223387억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 223444억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 229550억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 229661억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 230991억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 231772억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 229924억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 230745억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 227931억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 228737억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 224978억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 225771억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 221965억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 222128억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -6640,26 +6640,26 @@
         <v>0.710618</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.670631</v>
+        <v>0.671022</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.310227</v>
+        <v>0.310831</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.19707</v>
+        <v>0.201123</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.088856</v>
+        <v>0.09277199999999999</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.020348</v>
+        <v>0.02371</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.019923</v>
+        <v>-0.016945</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.039077</v>
+        <v>-0.041587</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6789,29 +6789,29 @@
         <v>0.104979</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.104968</v>
+        <v>0.104943</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.104942</v>
+        <v>0.104945</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.104952</v>
+        <v>0.104964</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.104961</v>
+        <v>0.104957</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.104983</v>
+        <v>0.104979</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.104985</v>
+        <v>0.104984</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.104975</v>
+        <v>0.10498</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6944,29 +6944,29 @@
         <v>0.029297</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.029329</v>
+        <v>0.029322</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.029296</v>
+        <v>0.029333</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.029328</v>
+        <v>0.02931</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.029335</v>
+        <v>0.029323</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.02934</v>
+        <v>0.029328</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.029316</v>
+        <v>0.029318</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.029332</v>
+        <v>0.029309</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7686,23 +7686,23 @@
         <v>0.049612</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.05059</v>
+        <v>0.050505</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.049865</v>
+        <v>0.049731</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.050459</v>
+        <v>0.050305</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.049401</v>
+        <v>0.050746</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.050676</v>
+        <v>0.050505</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>0.049724</v>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
         <v>0</v>
@@ -8113,13 +8113,13 @@
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8231,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
         <v>0</v>
@@ -8241,13 +8241,13 @@
         <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8470,20 +8470,20 @@
         <v>0.107062</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.120713</v>
+        <v>0.121228</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.095012</v>
+        <v>0.095275</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.088724</v>
+        <v>0.08894199999999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.07212499999999999</v>
+        <v>0.07231700000000001</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.082356</v>
+        <v>0.08226700000000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8598,20 +8598,20 @@
         <v>0.107062</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.120713</v>
+        <v>0.121228</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.095012</v>
+        <v>0.095275</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.088724</v>
+        <v>0.08894199999999999</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.07212499999999999</v>
+        <v>0.07231700000000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.082356</v>
+        <v>0.08226700000000001</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9244,26 +9244,26 @@
         <v>-0.533528</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.57987</v>
+        <v>-0.580519</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.52085</v>
+        <v>-0.521637</v>
       </c>
       <c r="AI41" s="24" t="n">
         <v>-0.217862</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.117188</v>
+        <v>-0.11875</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.134467</v>
+        <v>-0.134675</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.078818</v>
+        <v>-0.080592</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.022491</v>
+        <v>-0.025952</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9667,29 +9667,29 @@
         <v>0.029297</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.029329</v>
+        <v>0.029322</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.029296</v>
+        <v>0.029333</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.029328</v>
+        <v>0.02931</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.029335</v>
+        <v>0.029323</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.02934</v>
+        <v>0.029328</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.029316</v>
+        <v>0.029318</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.029332</v>
+        <v>0.029309</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -31024,7 +31024,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>303.7</v>
+        <v>303.8</v>
       </c>
     </row>
     <row r="30">
@@ -31044,7 +31044,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 223444억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 224358억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 229661억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 233999억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 231772억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 243296억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 230745억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 254117억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 228737억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 268264억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 225771억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 284403억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 222128억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
+고객지수 4분기 이동합(t−2) 301487억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -924,25 +924,25 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 65억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 66억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 72억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 73억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 78억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 80억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 84억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 87억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1815,43 +1815,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 223444억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 224358억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 229661억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 233999억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 231772억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 243296억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 230745억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 254117억 × 비례계수 0.0038 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 228737억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 268264억 × 비례계수 0.0038 × 계절비중 Q2 0.252(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 225771억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 284403억 × 비례계수 0.0038 × 계절비중 Q3 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 222128억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−2) 301487억 × 비례계수 0.0038 × 계절비중 Q4 0.279(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.89, n=14, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2288,25 +2288,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 65억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 66억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 72억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 73억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 78억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 80억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 84억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 87억 × 1.58% − 총차입금 0억 × 4.49% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4454,7 +4454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 18.5, "op_wape_pct": 205.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 127.59, "rev_act": 116.42, "op_pred": 7.65, "op_act": 3.7}, {"q": "2025Q4", "rev_pred": 163.85, "rev_act": 125.9, "op_pred": 9.82, "op_act": -1.02}, {"q": "2026Q1", "rev_pred": 132.61, "rev_act": 114.94, "op_pred": 7.95, "op_act": 3.09}, {"q": "2026Q2", "rev_pred": 151.15, "rev_act": 127.96, "op_pred": 9.06, "op_act": 4.15}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 18.5, "op_wape_pct": 205.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 11.8, "wape_trend": 11.2, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 127.59, "rev_act": 116.42, "op_pred": 7.65, "op_act": 3.7}, {"q": "2025Q4", "rev_pred": 163.85, "rev_act": 125.9, "op_pred": 9.82, "op_act": -1.02}, {"q": "2026Q1", "rev_pred": 132.61, "rev_act": 114.94, "op_pred": 7.95, "op_act": 3.09}, {"q": "2026Q2", "rev_pred": 151.15, "rev_act": 127.96, "op_pred": 9.06, "op_act": 4.15}]}</t>
         </is>
       </c>
     </row>
@@ -6640,26 +6640,26 @@
         <v>0.710618</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.671022</v>
+        <v>0.677899</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.310831</v>
+        <v>0.335593</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.201123</v>
+        <v>0.26084</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.09277199999999999</v>
+        <v>0.203448</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.02371</v>
+        <v>0.195706</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.016945</v>
+        <v>0.215395</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.041587</v>
+        <v>0.239176</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6789,29 +6789,29 @@
         <v>0.104979</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.104943</v>
+        <v>0.104979</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.104945</v>
+        <v>0.104959</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.104964</v>
+        <v>0.104949</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.104957</v>
+        <v>0.104941</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.104979</v>
+        <v>0.104974</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.104984</v>
+        <v>0.104961</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.10498</v>
+        <v>0.104975</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6944,29 +6944,29 @@
         <v>0.029297</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.029322</v>
+        <v>0.029342</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.029333</v>
+        <v>0.029342</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.02931</v>
+        <v>0.029316</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.029323</v>
+        <v>0.029331</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.029328</v>
+        <v>0.02933</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.029318</v>
+        <v>0.02931</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.029309</v>
+        <v>0.029314</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7234,13 +7234,13 @@
         <v>0.26</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7683,29 +7683,29 @@
         <v>0.05059</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.049612</v>
+        <v>0.049383</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.050505</v>
+        <v>0.049669</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.049731</v>
+        <v>0.05</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.050305</v>
+        <v>0.05</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.050746</v>
+        <v>0.049936</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.050505</v>
+        <v>0.049933</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.049724</v>
+        <v>0.05036</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8100,10 +8100,10 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI31" s="29" t="n">
         <v>0</v>
@@ -8228,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AH32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI32" s="29" t="n">
         <v>0</v>
@@ -8464,26 +8464,26 @@
         <v>0.137586</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.131686</v>
+        <v>0.132331</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.107062</v>
+        <v>0.108898</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.121228</v>
+        <v>0.126775</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.095275</v>
+        <v>0.103857</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.08894199999999999</v>
+        <v>0.102063</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.07231700000000001</v>
+        <v>0.087868</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.08226700000000001</v>
+        <v>0.106012</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8592,26 +8592,26 @@
         <v>0.137586</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.131686</v>
+        <v>0.132331</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.107062</v>
+        <v>0.108898</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.121228</v>
+        <v>0.126775</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.095275</v>
+        <v>0.103857</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.08894199999999999</v>
+        <v>0.102063</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.07231700000000001</v>
+        <v>0.087868</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.08226700000000001</v>
+        <v>0.106012</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9247,23 +9247,23 @@
         <v>-0.580519</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.521637</v>
+        <v>-0.523997</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.217862</v>
+        <v>-0.232747</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.11875</v>
+        <v>-0.154687</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.134675</v>
+        <v>-0.201238</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.080592</v>
+        <v>-0.186777</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.025952</v>
+        <v>-0.183422</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9379,7 +9379,7 @@
         <v>-0.04</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="AN42" s="24" t="n">
         <v>-0.041667</v>
@@ -9667,29 +9667,29 @@
         <v>0.029297</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.029322</v>
+        <v>0.029342</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.029333</v>
+        <v>0.029342</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.02931</v>
+        <v>0.029316</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.029323</v>
+        <v>0.029331</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.029328</v>
+        <v>0.02933</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.029318</v>
+        <v>0.02931</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.029309</v>
+        <v>0.029314</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31024,7 +31024,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>303.8</v>
+        <v>304.1</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4344,7 +4344,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5215,35 +5215,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5334,35 +5334,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5453,35 +5453,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5572,35 +5572,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5691,35 +5691,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5810,35 +5810,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5929,35 +5929,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6048,35 +6048,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6168,7 +6168,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1402</v>
+        <v>1473</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6396,7 +6396,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1422.5</v>
+        <v>1439.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>1402</v>
+        <v>1473</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.01612875992847357</v>
+        <v>0.01612875992847337</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0116538536404746</v>
+        <v>0.01165385364047455</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31641,7 +31641,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.17</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4344,7 +4344,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5215,35 +5215,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5334,35 +5334,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5453,35 +5453,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5572,35 +5572,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5691,35 +5691,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5810,35 +5810,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5929,35 +5929,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6048,35 +6048,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6168,7 +6168,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1473</v>
+        <v>1535</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6396,7 +6396,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1439.3</v>
+        <v>1463.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9242,11 +9242,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>1473</v>
+        <v>1535</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,443원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,402원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31641,7 +31641,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.69</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="32">
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4344,7 +4344,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -5215,35 +5215,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5334,35 +5334,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5453,35 +5453,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5572,35 +5572,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5691,35 +5691,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5810,35 +5810,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5929,35 +5929,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6048,35 +6048,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6168,7 +6168,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1535</v>
+        <v>1645</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6396,7 +6396,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1463.2</v>
+        <v>1499.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9242,11 +9242,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>1535</v>
+        <v>1645</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,402원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,473원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31641,7 +31641,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.14</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="32">
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1016,62 +1016,62 @@
     </comment>
     <comment ref="AC27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0(r4)
+max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AD27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0(r4)
+max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AF27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0275(r4)
+max(세전, 0) × 세율 2.8%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AG27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.055(r4)
+max(세전, 0) × 세율 5.5%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AH27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0825(r4)
+max(세전, 0) × 세율 8.2%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AI27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.11(r4)
+max(세전, 0) × 세율 11.0%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AK27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1375(r4)
+max(세전, 0) × 세율 13.8%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AL27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.165(r4)
+max(세전, 0) × 세율 16.5%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AM27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1925(r4)
+max(세전, 0) × 세율 19.2%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AN27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.22(r4)
+max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AC28" authorId="0" shapeId="0">
@@ -1614,79 +1614,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN39" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI40" authorId="0" shapeId="0">
+    <comment ref="AI39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN40" authorId="0" shapeId="0">
+    <comment ref="AN39" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -2070,55 +2010,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 33억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 34억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 36억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 37억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 38억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 40억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 41억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
-[identity]</t>
-      </text>
-    </comment>
-    <comment ref="AI11" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 43억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
-    <comment ref="AK11" authorId="0" shapeId="0">
+    <comment ref="AI11" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 46억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
+    <comment ref="AK11" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 49억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+[identity]</t>
+      </text>
+    </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 48억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 52억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 51억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 54억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 53억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 57억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2130,55 +2070,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 33억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 36억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 37억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 40억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 이자발생자산 41억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
-[interest]</t>
-      </text>
-    </comment>
-    <comment ref="AI12" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자발생자산 43억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
-    <comment ref="AK12" authorId="0" shapeId="0">
+    <comment ref="AI12" authorId="0" shapeId="0">
       <text>
         <t>추정: 이자발생자산 46억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
+    <comment ref="AK12" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 이자발생자산 49억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+[interest]</t>
+      </text>
+    </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 51억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 53억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57억 × 1.58%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)) − 총차입금 152억 × 1.16%(CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2429,61 +2369,61 @@
     </comment>
     <comment ref="AC17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AD17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.0%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AF17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 2.8%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AG17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 5.5%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AH17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 8.2%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AI17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 11.0%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AK17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 13.8%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AL17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 16.5%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AM17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 19.2%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AN17" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
@@ -3342,159 +3282,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="Y32" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI -2억 − (비영업손익 -7억 − 12분기 기준선 1억) × (1 − 22.0%, 모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)) × 지배 비중 1.00(그 분기 지배NI/NI) = 4억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS -30.0원</t>
-      </text>
-    </comment>
-    <comment ref="AA32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AB32" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 -7억 × (1 − 세율 0.0% [모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = 5억 ÷ 유통주식수 · 초과 = 비영업손익 -7억 − 12분기 기준선 1억 · 보고 EPS -30원(EPS 행 불변) · 상수 -7.44·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN32" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC33" authorId="0" shapeId="0">
@@ -4328,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4344,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4232,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4322,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 0% → 22%(terminal, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프) — 이월결손 램프(assumptions.tax_schedule): 변수 drv:법인세비용 추정 분기 셀이 분기별 세율(3절 '세율' 스칼라 연결 안 됨 — 그 값은 시작 세율) · 근거: 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4343,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.61% / 부채 1.17% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0158, 0.0116] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)"}</t>
+          <t>· 이자율 자산 1.55% / 부채 1.15% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0158, 0.0116] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 1분기 &lt; 4)", "debt": "CF 이자지급 ÷ 평균 총차입금(2023Q1~2025Q1; 주석 이자비용 1분기 &lt; 4)"}</t>
         </is>
       </c>
     </row>
@@ -4507,50 +4357,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2025Q4 보고 -30→조정 73원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(이월결손 램프(assumptions.tax_schedule, 0%→22%) — 분기별 세율 드라이버 행 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 5.0/8.3/10.2배(hist_quarterly(분기 평균가 ÷ TTM EPS, 14분기, 25/50/75 백분위)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/103230.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/103230.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 22.6% &gt; 추세 18.8% × 1.10 (suppliers_mentions·시차 2·4분기 이동합·창 19, r=0.89 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 -7억(영업이익 -1억의 7배, 12분기 중위 1억·기준선 1억) → 지배NI -2억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 50.6원(보고 -30.0원; 초과 비영업손익 -7억 × (1 − 세율 22.0%) × 지배 비중 1.00 = -6억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -0/+0/+0/+0(중위 +0억) → 추정 2026Q3 -0억(차 -0억, -401%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 22.6% &gt; 추세 18.8% × 1.10 (suppliers_mentions·시차 2·4분기 이동합·창 19, r=0.89 유의)): 전년동기 × (1+g) 추세 / 법인세율 이월결손 경로: 최근 양(+)세전 6분기 유효세율 중위 -35.1% → 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2025Q4: 비영업손익 -7억(영업이익 -1억의 7배, 12분기 중위 1억·기준선 1억) → 지배NI -2억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 73.3원(보고 -30.0원; 초과 비영업손익 -7억 × (1 − 세율 0.0%) × 지배 비중 1.00 = -7억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -0/+0/+0/+0(중위 +0억) → 추정 2026Q3 -0억(차 -0억, -401%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 18.5, "op_wape_pct": 205.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 11.8, "wape_trend": 11.2, "adopted": true, "decision": "adopted"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 127.59, "rev_act": 116.42, "op_pred": 7.65, "op_act": 3.7}, {"q": "2025Q4", "rev_pred": 163.85, "rev_act": 125.9, "op_pred": 9.82, "op_act": -1.02}, {"q": "2026Q1", "rev_pred": 132.61, "rev_act": 114.94, "op_pred": 7.95, "op_act": 3.09}, {"q": "2026Q2", "rev_pred": 151.15, "rev_act": 127.96, "op_pred": 9.06, "op_act": 4.15}]}</t>
         </is>
@@ -4567,7 +4424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6694,11 +6551,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6706,19 +6563,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6726,19 +6583,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -7379,7 +7236,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 세율</t>
+          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 분기별 세율(이월결손 램프, assumptions.tax_schedule)</t>
         </is>
       </c>
       <c r="E27" s="21">
@@ -7478,53 +7335,43 @@
         <f>IFERROR(subQ!AB17/subQ!AB16,"")</f>
         <v/>
       </c>
-      <c r="AC27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AD27" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AC27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE17/subQ!AE16,"")</f>
         <v/>
       </c>
-      <c r="AF27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AG27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AH27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AI27" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AF27" s="24" t="n">
+        <v>0.026578073</v>
+      </c>
+      <c r="AG27" s="24" t="n">
+        <v>0.056047198</v>
+      </c>
+      <c r="AH27" s="24" t="n">
+        <v>0.082236842</v>
+      </c>
+      <c r="AI27" s="24" t="n">
+        <v>0.111445783</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ17/subQ!AJ16,"")</f>
         <v/>
       </c>
-      <c r="AK27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AL27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AM27" s="26">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="AN27" s="26">
-        <f>$D$50</f>
-        <v/>
+      <c r="AK27" s="24" t="n">
+        <v>0.139072848</v>
+      </c>
+      <c r="AL27" s="24" t="n">
+        <v>0.164705882</v>
+      </c>
+      <c r="AM27" s="24" t="n">
+        <v>0.19218241</v>
+      </c>
+      <c r="AN27" s="24" t="n">
+        <v>0.220895522</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO17/subQ!AO16,"")</f>
@@ -7644,11 +7491,11 @@
         <v/>
       </c>
       <c r="AC28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AD28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AE28" s="25">
@@ -7656,19 +7503,19 @@
         <v/>
       </c>
       <c r="AF28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AG28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AH28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AI28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AJ28" s="25">
@@ -7676,19 +7523,19 @@
         <v/>
       </c>
       <c r="AK28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AL28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AM28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AN28" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AO28" s="25">
@@ -7919,36 +7766,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>-0.001084398</v>
+        <v>0.005180418</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.011542335</v>
+        <v>0.001460245</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.009935497</v>
+        <v>-0.005600626</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.003814284</v>
+        <v>0.005252865</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.003526412</v>
+        <v>-0.00190339</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.008458134000000001</v>
+        <v>-0.011151955</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.00789516</v>
+        <v>-0.009881480999999999</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.006154794</v>
+        <v>0.000183645</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.006988009</v>
+        <v>0.000961695</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.005066322</v>
+        <v>0.000600254</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -8047,36 +7894,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.001084398</v>
+        <v>0.005180418</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.011542335</v>
+        <v>0.001460245</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.009935497</v>
+        <v>-0.005600626</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>0.003814284</v>
+        <v>0.005252865</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.003526412</v>
+        <v>-0.00190339</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.008458134000000001</v>
+        <v>-0.011151955</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.00789516</v>
+        <v>-0.009881480999999999</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>-0.006154794</v>
+        <v>0.000183645</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.006988009</v>
+        <v>0.000961695</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.005066322</v>
+        <v>0.000600254</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8303,36 +8150,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>-0.019440122</v>
+        <v>-0.024868486</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>-0.021640664</v>
+        <v>-0.027918354</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>-0.020061728</v>
+        <v>-0.025422993</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>-0.023097113</v>
+        <v>-0.028490028</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>-0.02113559</v>
+        <v>-0.025568182</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>-0.023696249</v>
+        <v>-0.027837863</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>-0.021928592</v>
+        <v>-0.025249105</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>-0.025390438</v>
+        <v>-0.028185788</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>-0.023397562</v>
+        <v>-0.025326797</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>-0.02617274</v>
+        <v>-0.027347024</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8431,36 +8278,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.07669942</v>
+        <v>0.09811658700000001</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.07775768500000001</v>
+        <v>0.097813239</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.06543624200000001</v>
+        <v>0.07886944799999999</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.06929133899999999</v>
+        <v>0.07984031900000001</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.057928326</v>
+        <v>0.064463956</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.060092807</v>
+        <v>0.064250054</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.051214708</v>
+        <v>0.053232715</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.05517385</v>
+        <v>0.054996127</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.046961326</v>
+        <v>0.045521292</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.049001131</v>
+        <v>0.045821629</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8921,264 +8768,176 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21">
-        <f>IFERROR(subQ!J32/subQ!E32-1,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="22" t="n"/>
-      <c r="L39" s="21">
-        <f>IFERROR(subQ!L32/subQ!G32-1,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="21">
-        <f>IFERROR(subQ!M32/subQ!H32-1,"")</f>
-        <v/>
-      </c>
-      <c r="N39" s="21">
-        <f>IFERROR(subQ!N32/subQ!I32-1,"")</f>
-        <v/>
-      </c>
-      <c r="O39" s="21">
-        <f>IFERROR(subQ!O32/subQ!J32-1,"")</f>
-        <v/>
-      </c>
-      <c r="P39" s="22" t="n"/>
-      <c r="Q39" s="21">
-        <f>IFERROR(subQ!Q32/subQ!L32-1,"")</f>
-        <v/>
-      </c>
-      <c r="R39" s="21">
-        <f>IFERROR(subQ!R32/subQ!M32-1,"")</f>
-        <v/>
-      </c>
-      <c r="S39" s="21">
-        <f>IFERROR(subQ!S32/subQ!N32-1,"")</f>
-        <v/>
-      </c>
-      <c r="T39" s="21">
-        <f>IFERROR(subQ!T32/subQ!O32-1,"")</f>
-        <v/>
-      </c>
-      <c r="U39" s="22" t="n"/>
-      <c r="V39" s="21">
-        <f>IFERROR(subQ!V32/subQ!Q32-1,"")</f>
-        <v/>
-      </c>
-      <c r="W39" s="21">
-        <f>IFERROR(subQ!W32/subQ!R32-1,"")</f>
-        <v/>
-      </c>
-      <c r="X39" s="21">
-        <f>IFERROR(subQ!X32/subQ!S32-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y39" s="21">
-        <f>IFERROR(subQ!Y32/subQ!T32-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z39" s="22" t="n"/>
-      <c r="AA39" s="21">
-        <f>IFERROR(subQ!AA32/subQ!V32-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB39" s="23">
-        <f>IFERROR(subQ!AB32/subQ!W32-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC39" s="24" t="n">
-        <v>-0.7431480029999999</v>
-      </c>
-      <c r="AD39" s="24" t="n">
-        <v>-0.292490119</v>
-      </c>
-      <c r="AE39" s="25" t="n"/>
-      <c r="AF39" s="24" t="n">
-        <v>-0.121621622</v>
-      </c>
-      <c r="AG39" s="24" t="n">
-        <v>-0.583900227</v>
-      </c>
-      <c r="AH39" s="24" t="n">
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E39" s="27">
+        <f>subQ!E34</f>
+        <v/>
+      </c>
+      <c r="F39" s="28">
+        <f>subQ!F34</f>
+        <v/>
+      </c>
+      <c r="G39" s="27">
+        <f>subQ!G34</f>
+        <v/>
+      </c>
+      <c r="H39" s="27">
+        <f>subQ!H34</f>
+        <v/>
+      </c>
+      <c r="I39" s="27">
+        <f>subQ!I34</f>
+        <v/>
+      </c>
+      <c r="J39" s="27">
+        <f>subQ!J34</f>
+        <v/>
+      </c>
+      <c r="K39" s="28">
+        <f>subQ!K34</f>
+        <v/>
+      </c>
+      <c r="L39" s="27">
+        <f>subQ!L34</f>
+        <v/>
+      </c>
+      <c r="M39" s="27">
+        <f>subQ!M34</f>
+        <v/>
+      </c>
+      <c r="N39" s="27">
+        <f>subQ!N34</f>
+        <v/>
+      </c>
+      <c r="O39" s="27">
+        <f>subQ!O34</f>
+        <v/>
+      </c>
+      <c r="P39" s="28">
+        <f>subQ!P34</f>
+        <v/>
+      </c>
+      <c r="Q39" s="27">
+        <f>subQ!Q34</f>
+        <v/>
+      </c>
+      <c r="R39" s="27">
+        <f>subQ!R34</f>
+        <v/>
+      </c>
+      <c r="S39" s="27">
+        <f>subQ!S34</f>
+        <v/>
+      </c>
+      <c r="T39" s="27">
+        <f>subQ!T34</f>
+        <v/>
+      </c>
+      <c r="U39" s="28">
+        <f>subQ!U34</f>
+        <v/>
+      </c>
+      <c r="V39" s="27">
+        <f>subQ!V34</f>
+        <v/>
+      </c>
+      <c r="W39" s="27">
+        <f>subQ!W34</f>
+        <v/>
+      </c>
+      <c r="X39" s="27">
+        <f>subQ!X34</f>
+        <v/>
+      </c>
+      <c r="Y39" s="27">
+        <f>subQ!Y34</f>
+        <v/>
+      </c>
+      <c r="Z39" s="28">
+        <f>subQ!Z34</f>
+        <v/>
+      </c>
+      <c r="AA39" s="27">
+        <f>subQ!AA34</f>
+        <v/>
+      </c>
+      <c r="AB39" s="29">
+        <f>subQ!AB34</f>
+        <v/>
+      </c>
+      <c r="AC39" s="33" t="n"/>
+      <c r="AD39" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" s="24" t="n">
-        <v>0.002793296</v>
-      </c>
-      <c r="AJ39" s="25" t="n"/>
-      <c r="AK39" s="24" t="n">
-        <v>0.003076923</v>
-      </c>
-      <c r="AL39" s="24" t="n">
+      <c r="AE39" s="31">
+        <f>subQ!AE34</f>
+        <v/>
+      </c>
+      <c r="AF39" s="33" t="n"/>
+      <c r="AG39" s="33" t="n"/>
+      <c r="AH39" s="33" t="n"/>
+      <c r="AI39" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AM39" s="24" t="n">
-        <v>0.009146341000000001</v>
-      </c>
-      <c r="AN39" s="24" t="n">
-        <v>0.005571031</v>
-      </c>
-      <c r="AO39" s="25" t="n"/>
+      <c r="AJ39" s="31">
+        <f>subQ!AJ34</f>
+        <v/>
+      </c>
+      <c r="AK39" s="33" t="n"/>
+      <c r="AL39" s="33" t="n"/>
+      <c r="AM39" s="33" t="n"/>
+      <c r="AN39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="31">
+        <f>subQ!AO34</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E40" s="27">
-        <f>subQ!E34</f>
-        <v/>
-      </c>
-      <c r="F40" s="28">
-        <f>subQ!F34</f>
-        <v/>
-      </c>
-      <c r="G40" s="27">
-        <f>subQ!G34</f>
-        <v/>
-      </c>
-      <c r="H40" s="27">
-        <f>subQ!H34</f>
-        <v/>
-      </c>
-      <c r="I40" s="27">
-        <f>subQ!I34</f>
-        <v/>
-      </c>
-      <c r="J40" s="27">
-        <f>subQ!J34</f>
-        <v/>
-      </c>
-      <c r="K40" s="28">
-        <f>subQ!K34</f>
-        <v/>
-      </c>
-      <c r="L40" s="27">
-        <f>subQ!L34</f>
-        <v/>
-      </c>
-      <c r="M40" s="27">
-        <f>subQ!M34</f>
-        <v/>
-      </c>
-      <c r="N40" s="27">
-        <f>subQ!N34</f>
-        <v/>
-      </c>
-      <c r="O40" s="27">
-        <f>subQ!O34</f>
-        <v/>
-      </c>
-      <c r="P40" s="28">
-        <f>subQ!P34</f>
-        <v/>
-      </c>
-      <c r="Q40" s="27">
-        <f>subQ!Q34</f>
-        <v/>
-      </c>
-      <c r="R40" s="27">
-        <f>subQ!R34</f>
-        <v/>
-      </c>
-      <c r="S40" s="27">
-        <f>subQ!S34</f>
-        <v/>
-      </c>
-      <c r="T40" s="27">
-        <f>subQ!T34</f>
-        <v/>
-      </c>
-      <c r="U40" s="28">
-        <f>subQ!U34</f>
-        <v/>
-      </c>
-      <c r="V40" s="27">
-        <f>subQ!V34</f>
-        <v/>
-      </c>
-      <c r="W40" s="27">
-        <f>subQ!W34</f>
-        <v/>
-      </c>
-      <c r="X40" s="27">
-        <f>subQ!X34</f>
-        <v/>
-      </c>
-      <c r="Y40" s="27">
-        <f>subQ!Y34</f>
-        <v/>
-      </c>
-      <c r="Z40" s="28">
-        <f>subQ!Z34</f>
-        <v/>
-      </c>
-      <c r="AA40" s="27">
-        <f>subQ!AA34</f>
-        <v/>
-      </c>
-      <c r="AB40" s="29">
-        <f>subQ!AB34</f>
-        <v/>
-      </c>
-      <c r="AC40" s="33" t="n"/>
-      <c r="AD40" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="31">
-        <f>subQ!AE34</f>
-        <v/>
-      </c>
-      <c r="AF40" s="33" t="n"/>
-      <c r="AG40" s="33" t="n"/>
-      <c r="AH40" s="33" t="n"/>
-      <c r="AI40" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="31">
-        <f>subQ!AJ34</f>
-        <v/>
-      </c>
-      <c r="AK40" s="33" t="n"/>
-      <c r="AL40" s="33" t="n"/>
-      <c r="AM40" s="33" t="n"/>
-      <c r="AN40" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="31">
-        <f>subQ!AO34</f>
-        <v/>
-      </c>
+      <c r="F40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="Z40" s="9" t="n"/>
+      <c r="AB40" s="5" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="10" t="n"/>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="11" t="n"/>
+      <c r="AK40" s="10" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="10" t="n"/>
+      <c r="AN40" s="10" t="n"/>
+      <c r="AO40" s="11" t="n"/>
     </row>
     <row r="41">
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F41" s="9" t="n"/>
       <c r="K41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
@@ -9200,14 +8959,22 @@
       <c r="AO41" s="11" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="n">
+        <v>1645</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,473원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9233,20 +9000,22 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D43" s="34" t="n">
-        <v>1645</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,473원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9272,22 +9041,20 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9313,20 +9080,20 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 14분기, 25/50/75 백분위)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9352,20 +9119,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D46" s="30" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 14분기, 25/50/75 백분위)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9391,20 +9158,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D47" s="30" t="n">
-        <v>8.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9430,20 +9197,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D48" s="30" t="n">
-        <v>10.2</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9469,20 +9236,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="n">
+        <v>0</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: 이월결손 램프(assumptions.tax_schedule, 0%→22%) — 분기별 세율 드라이버 행 사용) — 모델 assumptions 값(시작 0% → terminal 22%, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프 — 분기별 값은 2절 drv:법인세비용 행) · 최근 8분기 중 세전 &gt; 0 인 6분기(2024Q4~2026Q2) 법인세/세전 중위 -35.1%·최근 4분기 중위 -35.1% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.0% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9508,20 +9275,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.2200251098556183</v>
+        <v>0.1049707849944957</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 -27.3% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -35.1% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.105)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9547,20 +9314,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1049707849944957</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.105)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9586,20 +9353,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>1</v>
+        <v>0.01545159234920223</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0158)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9625,20 +9392,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.01612875992847337</v>
+        <v>0.01152913900412491</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0158)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0116)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -9664,20 +9431,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="n">
-        <v>0.01165385364047455</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0116)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -9703,20 +9470,18 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -9742,18 +9507,18 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D56" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -9779,15 +9544,15 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -9812,43 +9577,6 @@
       <c r="AM57" s="10" t="n"/>
       <c r="AN57" s="10" t="n"/>
       <c r="AO57" s="11" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
-      <c r="P58" s="9" t="n"/>
-      <c r="U58" s="9" t="n"/>
-      <c r="Z58" s="9" t="n"/>
-      <c r="AB58" s="5" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="11" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="11" t="n"/>
-      <c r="AK58" s="10" t="n"/>
-      <c r="AL58" s="10" t="n"/>
-      <c r="AM58" s="10" t="n"/>
-      <c r="AN58" s="10" t="n"/>
-      <c r="AO58" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10110,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10702,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19510,11 +19238,11 @@
       </c>
       <c r="AB12" s="19" t="n"/>
       <c r="AC12" s="20">
-        <f>IFERROR((AB26*변수!$D$53-AB24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AB26*변수!$D$52-AB24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC26*변수!$D$53-AC24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AC26*변수!$D$52-AC24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -19522,19 +19250,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD26*변수!$D$53-AD24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AD26*변수!$D$52-AD24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF26*변수!$D$53-AF24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AF26*변수!$D$52-AF24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG26*변수!$D$53-AG24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AG26*변수!$D$52-AG24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH26*변수!$D$53-AH24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AH26*변수!$D$52-AH24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -19542,19 +19270,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI26*변수!$D$53-AI24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AI26*변수!$D$52-AI24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK26*변수!$D$53-AK24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AK26*변수!$D$52-AK24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL26*변수!$D$53-AL24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AL26*변수!$D$52-AL24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM26*변수!$D$53-AM24*변수!$D$54)/4,"")</f>
+        <f>IFERROR((AM26*변수!$D$52-AM24*변수!$D$53)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -22621,86 +22349,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E32" s="18" t="n">
-        <v>152.2</v>
+      <c r="E32" s="18">
+        <f>IFERROR(E31,"")</f>
+        <v/>
       </c>
       <c r="F32" s="37" t="n"/>
-      <c r="G32" s="18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H32" s="18" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="I32" s="18" t="n">
-        <v>126</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>149.1</v>
+      <c r="G32" s="18">
+        <f>IFERROR(G31,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>IFERROR(H31,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>IFERROR(I31,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="18">
+        <f>IFERROR(J31,"")</f>
+        <v/>
       </c>
       <c r="K32" s="37">
         <f>SUM(G32:J32)</f>
         <v/>
       </c>
-      <c r="L32" s="18" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="M32" s="18" t="n">
-        <v>171.2</v>
-      </c>
-      <c r="N32" s="18" t="n">
-        <v>101</v>
-      </c>
-      <c r="O32" s="18" t="n">
-        <v>46.2</v>
+      <c r="L32" s="18">
+        <f>IFERROR(L31,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="18">
+        <f>IFERROR(M31,"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="18">
+        <f>IFERROR(N31,"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="18">
+        <f>IFERROR(O31,"")</f>
+        <v/>
       </c>
       <c r="P32" s="37">
         <f>SUM(L32:O32)</f>
         <v/>
       </c>
-      <c r="Q32" s="18" t="n">
-        <v>160.1</v>
-      </c>
-      <c r="R32" s="18" t="n">
-        <v>116.6</v>
-      </c>
-      <c r="S32" s="18" t="n">
-        <v>-60.5</v>
-      </c>
-      <c r="T32" s="18" t="n">
-        <v>445.1</v>
+      <c r="Q32" s="18">
+        <f>IFERROR(Q31,"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="18">
+        <f>IFERROR(R31,"")</f>
+        <v/>
+      </c>
+      <c r="S32" s="18">
+        <f>IFERROR(S31,"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="18">
+        <f>IFERROR(T31,"")</f>
+        <v/>
       </c>
       <c r="U32" s="37">
         <f>SUM(Q32:T32)</f>
         <v/>
       </c>
-      <c r="V32" s="18" t="n">
-        <v>256.3</v>
-      </c>
-      <c r="W32" s="18" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="X32" s="18" t="n">
-        <v>127.7</v>
-      </c>
-      <c r="Y32" s="20" t="n">
-        <v>50.6</v>
+      <c r="V32" s="18">
+        <f>IFERROR(V31,"")</f>
+        <v/>
+      </c>
+      <c r="W32" s="18">
+        <f>IFERROR(W31,"")</f>
+        <v/>
+      </c>
+      <c r="X32" s="18">
+        <f>IFERROR(X31,"")</f>
+        <v/>
+      </c>
+      <c r="Y32" s="20">
+        <f>IFERROR((Y19-(-7.44)*(1.0))*100/Y30,"")</f>
+        <v/>
       </c>
       <c r="Z32" s="37">
         <f>SUM(V32:Y32)</f>
         <v/>
       </c>
-      <c r="AA32" s="18" t="n">
-        <v>37</v>
-      </c>
-      <c r="AB32" s="19" t="n">
-        <v>88.2</v>
+      <c r="AA32" s="18">
+        <f>IFERROR(AA31,"")</f>
+        <v/>
+      </c>
+      <c r="AB32" s="19">
+        <f>IFERROR(AB31,"")</f>
+        <v/>
       </c>
       <c r="AC32" s="20">
-        <f>IFERROR(X32*(1+변수!AC39),"")</f>
+        <f>IFERROR(AC31,"")</f>
         <v/>
       </c>
       <c r="AD32" s="20">
-        <f>IFERROR(Y32*(1+변수!AD39),"")</f>
+        <f>IFERROR(AD31,"")</f>
         <v/>
       </c>
       <c r="AE32" s="38">
@@ -22708,19 +22455,19 @@
         <v/>
       </c>
       <c r="AF32" s="20">
-        <f>IFERROR(AA32*(1+변수!AF39),"")</f>
+        <f>IFERROR(AF31,"")</f>
         <v/>
       </c>
       <c r="AG32" s="20">
-        <f>IFERROR(AB32*(1+변수!AG39),"")</f>
+        <f>IFERROR(AG31,"")</f>
         <v/>
       </c>
       <c r="AH32" s="20">
-        <f>IFERROR(AC32*(1+변수!AH39),"")</f>
+        <f>IFERROR(AH31,"")</f>
         <v/>
       </c>
       <c r="AI32" s="20">
-        <f>IFERROR(AD32*(1+변수!AI39),"")</f>
+        <f>IFERROR(AI31,"")</f>
         <v/>
       </c>
       <c r="AJ32" s="38">
@@ -22728,19 +22475,19 @@
         <v/>
       </c>
       <c r="AK32" s="20">
-        <f>IFERROR(AF32*(1+변수!AK39),"")</f>
+        <f>IFERROR(AK31,"")</f>
         <v/>
       </c>
       <c r="AL32" s="20">
-        <f>IFERROR(AG32*(1+변수!AL39),"")</f>
+        <f>IFERROR(AL31,"")</f>
         <v/>
       </c>
       <c r="AM32" s="20">
-        <f>IFERROR(AH32*(1+변수!AM39),"")</f>
+        <f>IFERROR(AM31,"")</f>
         <v/>
       </c>
       <c r="AN32" s="20">
-        <f>IFERROR(AI32*(1+변수!AN39),"")</f>
+        <f>IFERROR(AN31,"")</f>
         <v/>
       </c>
       <c r="AO32" s="38">
@@ -22989,7 +22736,7 @@
       <c r="AB34" s="19" t="n"/>
       <c r="AC34" s="20" t="n"/>
       <c r="AD34" s="20">
-        <f>변수!AD40</f>
+        <f>변수!AD39</f>
         <v/>
       </c>
       <c r="AE34" s="38">
@@ -23000,7 +22747,7 @@
       <c r="AG34" s="20" t="n"/>
       <c r="AH34" s="20" t="n"/>
       <c r="AI34" s="20">
-        <f>변수!AI40</f>
+        <f>변수!AI39</f>
         <v/>
       </c>
       <c r="AJ34" s="38">
@@ -23011,7 +22758,7 @@
       <c r="AL34" s="20" t="n"/>
       <c r="AM34" s="20" t="n"/>
       <c r="AN34" s="20">
-        <f>변수!AN40</f>
+        <f>변수!AN39</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -23122,11 +22869,11 @@
         <v/>
       </c>
       <c r="AC35" s="39">
-        <f>IFERROR(변수!$D$43/(Y31+AA31+AB31+AC31),"")</f>
+        <f>IFERROR(변수!$D$42/(Y31+AA31+AB31+AC31),"")</f>
         <v/>
       </c>
       <c r="AD35" s="39">
-        <f>IFERROR(변수!$D$43/(AA31+AB31+AC31+AD31),"")</f>
+        <f>IFERROR(변수!$D$42/(AA31+AB31+AC31+AD31),"")</f>
         <v/>
       </c>
       <c r="AE35" s="40">
@@ -23134,19 +22881,19 @@
         <v/>
       </c>
       <c r="AF35" s="39">
-        <f>IFERROR(변수!$D$43/(AB31+AC31+AD31+AF31),"")</f>
+        <f>IFERROR(변수!$D$42/(AB31+AC31+AD31+AF31),"")</f>
         <v/>
       </c>
       <c r="AG35" s="39">
-        <f>IFERROR(변수!$D$43/(AC31+AD31+AF31+AG31),"")</f>
+        <f>IFERROR(변수!$D$42/(AC31+AD31+AF31+AG31),"")</f>
         <v/>
       </c>
       <c r="AH35" s="39">
-        <f>IFERROR(변수!$D$43/(AD31+AF31+AG31+AH31),"")</f>
+        <f>IFERROR(변수!$D$42/(AD31+AF31+AG31+AH31),"")</f>
         <v/>
       </c>
       <c r="AI35" s="39">
-        <f>IFERROR(변수!$D$43/(AF31+AG31+AH31+AI31),"")</f>
+        <f>IFERROR(변수!$D$42/(AF31+AG31+AH31+AI31),"")</f>
         <v/>
       </c>
       <c r="AJ35" s="40">
@@ -23154,19 +22901,19 @@
         <v/>
       </c>
       <c r="AK35" s="39">
-        <f>IFERROR(변수!$D$43/(AG31+AH31+AI31+AK31),"")</f>
+        <f>IFERROR(변수!$D$42/(AG31+AH31+AI31+AK31),"")</f>
         <v/>
       </c>
       <c r="AL35" s="39">
-        <f>IFERROR(변수!$D$43/(AH31+AI31+AK31+AL31),"")</f>
+        <f>IFERROR(변수!$D$42/(AH31+AI31+AK31+AL31),"")</f>
         <v/>
       </c>
       <c r="AM35" s="39">
-        <f>IFERROR(변수!$D$43/(AI31+AK31+AL31+AM31),"")</f>
+        <f>IFERROR(변수!$D$42/(AI31+AK31+AL31+AM31),"")</f>
         <v/>
       </c>
       <c r="AN35" s="39">
-        <f>IFERROR(변수!$D$43/(AK31+AL31+AM31+AN31),"")</f>
+        <f>IFERROR(변수!$D$42/(AK31+AL31+AM31+AN31),"")</f>
         <v/>
       </c>
       <c r="AO35" s="40">
@@ -23277,11 +23024,11 @@
         <v/>
       </c>
       <c r="AC36" s="39">
-        <f>IFERROR(변수!$D$43/AC33,"")</f>
+        <f>IFERROR(변수!$D$42/AC33,"")</f>
         <v/>
       </c>
       <c r="AD36" s="39">
-        <f>IFERROR(변수!$D$43/AD33,"")</f>
+        <f>IFERROR(변수!$D$42/AD33,"")</f>
         <v/>
       </c>
       <c r="AE36" s="40">
@@ -23289,19 +23036,19 @@
         <v/>
       </c>
       <c r="AF36" s="39">
-        <f>IFERROR(변수!$D$43/AF33,"")</f>
+        <f>IFERROR(변수!$D$42/AF33,"")</f>
         <v/>
       </c>
       <c r="AG36" s="39">
-        <f>IFERROR(변수!$D$43/AG33,"")</f>
+        <f>IFERROR(변수!$D$42/AG33,"")</f>
         <v/>
       </c>
       <c r="AH36" s="39">
-        <f>IFERROR(변수!$D$43/AH33,"")</f>
+        <f>IFERROR(변수!$D$42/AH33,"")</f>
         <v/>
       </c>
       <c r="AI36" s="39">
-        <f>IFERROR(변수!$D$43/AI33,"")</f>
+        <f>IFERROR(변수!$D$42/AI33,"")</f>
         <v/>
       </c>
       <c r="AJ36" s="40">
@@ -23309,19 +23056,19 @@
         <v/>
       </c>
       <c r="AK36" s="39">
-        <f>IFERROR(변수!$D$43/AK33,"")</f>
+        <f>IFERROR(변수!$D$42/AK33,"")</f>
         <v/>
       </c>
       <c r="AL36" s="39">
-        <f>IFERROR(변수!$D$43/AL33,"")</f>
+        <f>IFERROR(변수!$D$42/AL33,"")</f>
         <v/>
       </c>
       <c r="AM36" s="39">
-        <f>IFERROR(변수!$D$43/AM33,"")</f>
+        <f>IFERROR(변수!$D$42/AM33,"")</f>
         <v/>
       </c>
       <c r="AN36" s="39">
-        <f>IFERROR(변수!$D$43/AN33,"")</f>
+        <f>IFERROR(변수!$D$42/AN33,"")</f>
         <v/>
       </c>
       <c r="AO36" s="40">
@@ -24355,7 +24102,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D43</f>
+        <f>변수!D42</f>
         <v/>
       </c>
       <c r="W2" s="42" t="n"/>
@@ -29488,7 +29235,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D43</f>
+        <f>변수!D42</f>
         <v/>
       </c>
       <c r="I2" s="42" t="n"/>
@@ -31255,7 +31002,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D43</f>
+        <f>변수!D42</f>
         <v/>
       </c>
     </row>
@@ -31266,7 +31013,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
     </row>
@@ -31443,7 +31190,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D49+F7*(1-변수!D49),"")</f>
+        <f>IFERROR(E7*변수!D48+F7*(1-변수!D48),"")</f>
         <v/>
       </c>
     </row>
@@ -31454,7 +31201,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -31478,7 +31225,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -31502,7 +31249,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -31566,7 +31313,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
     </row>
@@ -31621,7 +31368,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>137.8</v>
+        <v>173.1</v>
       </c>
     </row>
     <row r="30">
@@ -31641,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.94</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="32">
@@ -31661,7 +31408,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0182</v>
+        <v>0.0228</v>
       </c>
     </row>
     <row r="34">
@@ -31671,7 +31418,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -31681,7 +31428,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="36">
@@ -33374,7 +33121,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D56</f>
+        <f>변수!D55</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,473원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,535원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.01545159234920223</v>
+        <v>0.01545159234920242</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.01152913900412491</v>
+        <v>0.01152913900412498</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1645</v>
+        <v>1520</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6253,7 +6253,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1499.6</v>
+        <v>1503</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1645</v>
+        <v>1520</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.5</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -31398,7 +31398,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1520</v>
+        <v>1507</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6253,7 +6253,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1503</v>
+        <v>1503.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8970,11 +8970,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1520</v>
+        <v>1507</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,535원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,645원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.779999999999999</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1507</v>
+        <v>1583</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6253,7 +6253,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1503.6</v>
+        <v>1513.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8970,11 +8970,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1507</v>
+        <v>1583</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,645원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,520원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.710000000000001</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="32">
@@ -31398,7 +31398,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1583</v>
+        <v>1539</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6253,7 +6253,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1513.5</v>
+        <v>1522.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8970,11 +8970,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1583</v>
+        <v>1539</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,520원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,531원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.15</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -31398,7 +31398,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/103230_model.xlsx
+++ b/argus/kship/models/103230_model.xlsx
@@ -4194,7 +4194,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5072,35 +5072,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5667,35 +5667,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5786,35 +5786,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5905,35 +5905,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1746</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6253,7 +6253,7 @@
         <v>2401.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1522.2</v>
+        <v>1527.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8970,11 +8970,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,531원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,559원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="32">
